--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:22</t>
+    <t xml:space="preserve">2026-09-09 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:18</t>
+    <t xml:space="preserve">2026-09-17 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -757,8 +757,12 @@
       <c r="C16" s="2" t="n">
         <v>4105</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="D16" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>601521</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:13</t>
+    <t xml:space="preserve">2026-09-23 12:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:42</t>
+    <t xml:space="preserve">2026-10-02 14:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:56</t>
+    <t xml:space="preserve">2026-10-04 09:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:13</t>
+    <t xml:space="preserve">2026-10-05 11:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
